--- a/00-TrainRnns/tau-9/Theta/BestModels-3tst.xlsx
+++ b/00-TrainRnns/tau-9/Theta/BestModels-3tst.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>R2_LSG_1_theta</t>
+          <t>R2_train_mean</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>R2_train_mean</t>
+          <t>R2_val_mean</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>R2_val_mean</t>
+          <t>R2_test_mean</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>R2_test_mean</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
@@ -482,197 +477,182 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>750</v>
+        <v>4384</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>model_arch26_r0.01_Ld0.5_Lp0.5_seed9468</t>
+          <t>model_arch41-18_r0.9_Ld0.7_Lp0.3_seed5920</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[26]</t>
+          <t>[41, 18]</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9284432230011667</v>
+        <v>0.9837985667099487</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9462809754884902</v>
+        <v>0.6141713565698301</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9214238476832146</v>
+        <v>0.01147382859759261</v>
       </c>
       <c r="G2" t="n">
-        <v>0.854492207885524</v>
+        <v>0.9837985667099487</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9284432230011667</v>
+        <v>0.6141713565698301</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9462809754884902</v>
+        <v>0.01147382859759261</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8879580277843693</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.9076685950375384</v>
+        <v>0.9837985667099487</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>756</v>
+        <v>3874</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>model_arch26_r0.9_Ld0.5_Lp0.5_seed9583</t>
+          <t>model_arch70-38_r0.9_Ld0.7_Lp0.3_seed5920</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[26]</t>
+          <t>[70, 38]</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9173822465458377</v>
+        <v>0.9798703434486253</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9534614624343881</v>
+        <v>-0.4259953079134455</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9249415827751415</v>
+        <v>0.451497415171852</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8455541495490204</v>
+        <v>0.9798703434486253</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9173822465458377</v>
+        <v>-0.4259953079134455</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9534614624343881</v>
+        <v>0.451497415171852</v>
       </c>
       <c r="J3" t="n">
-        <v>0.885247866162081</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.9049205697407937</v>
+        <v>0.9798703434486253</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>1503</v>
+        <v>5674</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>model_arch51_r0.01_Ld0.5_Lp0.5_seed134</t>
+          <t>model_arch51-30_r0.9_Ld0.5_Lp0.5_seed5396</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[51]</t>
+          <t>[51, 30]</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9398567422592758</v>
+        <v>0.9770789315131605</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9376451946033012</v>
+        <v>0.9359094293185484</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9473317823730201</v>
+        <v>0.708190554816582</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8086752679533186</v>
+        <v>0.9770789315131605</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9398567422592758</v>
+        <v>0.9359094293185484</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9376451946033012</v>
+        <v>0.708190554816582</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8780035251631693</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.9026570948095869</v>
+        <v>0.9770789315131605</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>1568</v>
+        <v>1298</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>model_arch53_r0.9_Ld0.5_Lp0.5_seed134</t>
+          <t>model_arch44_r0.9_Ld0.5_Lp0.5_seed134</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[53]</t>
+          <t>[44]</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9312452540225685</v>
+        <v>0.9767943777699738</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9428291330050368</v>
+        <v>0.849096748113082</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9268826169598813</v>
+        <v>0.9193777027945162</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8254038004038855</v>
+        <v>0.9767943777699738</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9312452540225685</v>
+        <v>0.849096748113082</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9428291330050368</v>
+        <v>0.9193777027945162</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8761432086818834</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.9021177116027885</v>
+        <v>0.9767943777699738</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>5727</v>
+        <v>3935</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>model_arch51-31_r0.9_Ld0.7_Lp0.3_seed3433</t>
+          <t>model_arch70-40_r0.9_Ld0.7_Lp0.3_seed3206</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[51, 31]</t>
+          <t>[70, 40]</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9045108215936819</v>
+        <v>0.9764145564194998</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9528132568587978</v>
+        <v>0.02772527843900185</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8930220442749788</v>
+        <v>0.8714687101483355</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8731584828415944</v>
+        <v>0.9764145564194998</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9045108215936819</v>
+        <v>0.02772527843900185</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9528132568587978</v>
+        <v>0.8714687101483355</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8830902635582866</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.9009501761559173</v>
+        <v>0.9764145564194998</v>
       </c>
     </row>
   </sheetData>

--- a/00-TrainRnns/tau-9/Theta/BestModels-3tst.xlsx
+++ b/00-TrainRnns/tau-9/Theta/BestModels-3tst.xlsx
@@ -477,182 +477,182 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>4384</v>
+        <v>3928</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>model_arch41-18_r0.9_Ld0.7_Lp0.3_seed5920</t>
+          <t>model_arch70-40_r0.01_Ld0.7_Lp0.3_seed3975</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[41, 18]</t>
+          <t>[70, 40]</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9837985667099487</v>
+        <v>0.9380947708020789</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6141713565698301</v>
+        <v>0.9768067909058848</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01147382859759261</v>
+        <v>0.955218211951019</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9837985667099487</v>
+        <v>0.9380947708020789</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6141713565698301</v>
+        <v>0.9768067909058848</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01147382859759261</v>
+        <v>0.955218211951019</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9837985667099487</v>
+        <v>0.8610359320976948</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>3874</v>
+        <v>3900</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>model_arch70-38_r0.9_Ld0.7_Lp0.3_seed5920</t>
+          <t>model_arch70-39_r0.01_Ld0.7_Lp0.3_seed3206</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[70, 38]</t>
+          <t>[70, 39]</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9798703434486253</v>
+        <v>0.9277389636815165</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4259953079134455</v>
+        <v>0.9702753189928974</v>
       </c>
       <c r="F3" t="n">
-        <v>0.451497415171852</v>
+        <v>0.9502274240544939</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9798703434486253</v>
+        <v>0.9277389636815165</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4259953079134455</v>
+        <v>0.9702753189928974</v>
       </c>
       <c r="I3" t="n">
-        <v>0.451497415171852</v>
+        <v>0.9502274240544939</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9798703434486253</v>
+        <v>0.8544725120186724</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>5674</v>
+        <v>3626</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>model_arch51-30_r0.9_Ld0.5_Lp0.5_seed5396</t>
+          <t>model_arch70-30_r0.01_Ld0.7_Lp0.3_seed8743</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[51, 30]</t>
+          <t>[70, 30]</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9770789315131605</v>
+        <v>0.9411096928345133</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9359094293185484</v>
+        <v>0.9558362732761464</v>
       </c>
       <c r="F4" t="n">
-        <v>0.708190554816582</v>
+        <v>0.9446240479139361</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9770789315131605</v>
+        <v>0.9411096928345133</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9359094293185484</v>
+        <v>0.9558362732761464</v>
       </c>
       <c r="I4" t="n">
-        <v>0.708190554816582</v>
+        <v>0.9446240479139361</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9770789315131605</v>
+        <v>0.8524710042073788</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>1298</v>
+        <v>3909</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>model_arch44_r0.9_Ld0.5_Lp0.5_seed134</t>
+          <t>model_arch70-40_r0.01_Ld0.5_Lp0.5_seed5920</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[44]</t>
+          <t>[70, 40]</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9767943777699738</v>
+        <v>0.9227400140761299</v>
       </c>
       <c r="E5" t="n">
-        <v>0.849096748113082</v>
+        <v>0.9724309863257787</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9193777027945162</v>
+        <v>0.942578748680334</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9767943777699738</v>
+        <v>0.9227400140761299</v>
       </c>
       <c r="H5" t="n">
-        <v>0.849096748113082</v>
+        <v>0.9724309863257787</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9193777027945162</v>
+        <v>0.942578748680334</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9767943777699738</v>
+        <v>0.8513249247246728</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>3935</v>
+        <v>4645</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>model_arch70-40_r0.9_Ld0.7_Lp0.3_seed3206</t>
+          <t>model_arch70-45_r0.9_Ld0.7_Lp0.3_seed7948</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[70, 40]</t>
+          <t>[70, 45]</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9764145564194998</v>
+        <v>0.9274269370358816</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02772527843900185</v>
+        <v>0.9489795359389968</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8714687101483355</v>
+        <v>0.9573276628155651</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9764145564194998</v>
+        <v>0.9274269370358816</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02772527843900185</v>
+        <v>0.9489795359389968</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8714687101483355</v>
+        <v>0.9573276628155651</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9764145564194998</v>
+        <v>0.850120240737133</v>
       </c>
     </row>
   </sheetData>
